--- a/site/leagues/proliga/2026_2027/xlsx/shot_packs/shot_pack_SLB.xlsx
+++ b/site/leagues/proliga/2026_2027/xlsx/shot_packs/shot_pack_SLB.xlsx
@@ -22,13 +22,13 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$W$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'alerts'!$A$1:$B$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'team_zones'!$A$1:$I$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -590,38 +590,38 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>110</v>
+        <v>173</v>
       </c>
       <c r="D2" t="n">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="E2" t="n">
-        <v>94</v>
+        <v>149</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>65</v>
+        <v>105</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -633,11 +633,11 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -646,15 +646,15 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="T2" t="n">
         <v>15</v>
@@ -663,7 +663,7 @@
         <v>14</v>
       </c>
       <c r="V2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="W2" t="n">
         <v>7</v>
@@ -681,11 +681,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -757,12 +757,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SLB_T._FILIPE</t>
+          <t>SLB_J._MENDES</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>T. Filipe</t>
+          <t>J. Mendes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -771,13 +771,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -789,11 +789,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
@@ -812,40 +812,310 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>8</v>
       </c>
       <c r="E3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>17.8%</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SLB_T._FILIPE</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>T. Filipe</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>13</v>
+      </c>
+      <c r="E4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>46.2%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>40.6%</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SLB_J._MENDES</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>J. Mendes</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>12</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>46.2%</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
         <v>2</v>
       </c>
-      <c r="F3" t="n">
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SLB_S._SOUSA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>S. Sousa</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>13</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>28.9%</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SLB_K._DOMINGUES</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>K. Domingues</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>12</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" t="n">
+        <v>8</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>63.2%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SLB_S._SOUSA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>S. Sousa</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>13</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>9</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>28.9%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SLB_T._FILIPE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>T. Filipe</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>9</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
         <v>6</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>28.1%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
         <v>2</v>
       </c>
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K3"/>
+  <autoFilter ref="A1:K9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -883,7 +1153,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Maior volume: S. Sousa (28 L)</t>
+          <t>Maior volume: S. Sousa (45 L)</t>
         </is>
       </c>
     </row>
@@ -895,7 +1165,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maior volume 3pt: S. Sousa (14 3PA)</t>
+          <t>Maior volume 3pt: S. Sousa (21 3PA)</t>
         </is>
       </c>
     </row>
@@ -907,7 +1177,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mais eficaz: M. Sousa (1.7 pts/shot)</t>
+          <t>Mais eficaz: M. Sousa (1.3 pts/shot)</t>
         </is>
       </c>
     </row>
@@ -919,7 +1189,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zona mais usada: Paint Non-RA (38 L)</t>
+          <t>Zona mais usada: Paint Non-RA (64 L)</t>
         </is>
       </c>
     </row>
@@ -931,7 +1201,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zona mais eficaz: Corner 3 Left (50.0%)</t>
+          <t>Zona mais eficaz: Corner 3 Left (54.5%)</t>
         </is>
       </c>
     </row>
@@ -1080,30 +1350,30 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E2" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -1111,35 +1381,35 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>13</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="L2" t="n">
-        <v>8</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
       <c r="O2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -1157,30 +1427,30 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
+        <v>23</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>31.2%</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
         <v>13</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>30.0%</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>7</v>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -1192,11 +1462,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1205,11 +1475,11 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -1219,7 +1489,7 @@
         <v>5</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -1234,66 +1504,66 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>57.7%</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>12</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>8</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>50.0%</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>7</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>6</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>66.7%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -1302,137 +1572,137 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SLB_K._DOMINGUES</t>
+          <t>SLB_M._SOUSA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>K. Domingues</t>
+          <t>M. Sousa</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" t="n">
+        <v>25</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>52.6%</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>11</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>57.9%</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
         <v>6</v>
       </c>
-      <c r="E5" t="n">
-        <v>12</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>46.2%</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>7.7%</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>7</v>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SLB_M._SOUSA</t>
+          <t>SLB_K._DOMINGUES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M. Sousa</t>
+          <t>K. Domingues</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="O6" t="n">
@@ -1440,17 +1710,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -1465,22 +1735,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>31.6%</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
         <v>4</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>22.2%</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>3</v>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -1488,43 +1758,43 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>21.1%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>7</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>6</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="J7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>3</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>3</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="Q7" t="n">
+        <v>4</v>
+      </c>
+      <c r="R7" t="n">
         <v>6</v>
-      </c>
-      <c r="R7" t="n">
-        <v>7</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1610,60 +1880,56 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SLB_W._SANTOS</t>
+          <t>SLB_G._VIEGAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>W. Santos</t>
+          <t>G. Viegas</t>
         </is>
       </c>
       <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
         <v>2</v>
       </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="O9" t="n">
@@ -1678,84 +1944,98 @@
         <v>8</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SLB_J._CORREIA</t>
+          <t>SLB_W._SANTOS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>J. Correia</t>
+          <t>W. Santos</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R10" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SLB_M._GONCALVES</t>
+          <t>SLB_J._CORREIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>M. Goncalves</t>
+          <t>J. Correia</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1786,32 +2066,22 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="O11" t="n">
-        <v>1</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
       <c r="Q11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R11" t="n">
         <v>8</v>
@@ -1823,16 +2093,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SLB_G._VIEGAS</t>
+          <t>SLB_M._GONCALVES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>G. Viegas</t>
+          <t>M. Goncalves</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -1870,11 +2140,21 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="Q12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="R12" t="n">
         <v>8</v>
@@ -1895,7 +2175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S6"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2028,42 +2308,42 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>19</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
+        <v>25</v>
+      </c>
+      <c r="H2" t="n">
         <v>11</v>
       </c>
-      <c r="F2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G2" t="n">
-        <v>19</v>
-      </c>
-      <c r="H2" t="n">
-        <v>8</v>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -2076,18 +2356,18 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -2096,12 +2376,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SLB_S._SOUSA</t>
+          <t>SLB_J._MENDES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>S. Sousa</t>
+          <t>J. Mendes</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -2109,62 +2389,62 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>57.7%</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>12</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
           <t>50.0%</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>8</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>7</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>42.9%</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
@@ -2173,89 +2453,89 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SLB_K._DOMINGUES</t>
+          <t>SLB_S._SOUSA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>K. Domingues</t>
+          <t>S. Sousa</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="E4" t="n">
+        <v>45</v>
+      </c>
+      <c r="F4" t="n">
+        <v>18</v>
+      </c>
+      <c r="G4" t="n">
+        <v>43</v>
+      </c>
+      <c r="H4" t="n">
+        <v>21</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
         <v>13</v>
       </c>
-      <c r="F4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G4" t="n">
-        <v>12</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>7.7%</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>7</v>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SLB_J._MENDES</t>
+          <t>SLB_K._DOMINGUES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>J. Mendes</t>
+          <t>K. Domingues</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -2263,65 +2543,65 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="E5" t="n">
+        <v>19</v>
+      </c>
+      <c r="F5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G5" t="n">
         <v>18</v>
       </c>
-      <c r="F5" t="n">
-        <v>7</v>
-      </c>
-      <c r="G5" t="n">
-        <v>16</v>
-      </c>
       <c r="H5" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -2340,29 +2620,29 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G6" t="n">
+        <v>23</v>
+      </c>
+      <c r="H6" t="n">
         <v>13</v>
       </c>
-      <c r="H6" t="n">
-        <v>7</v>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2371,11 +2651,11 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -2384,11 +2664,11 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -2401,8 +2681,85 @@
         <v>4</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SLB_W._OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>W. Oliveira</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>31.6%</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>19</v>
+      </c>
+      <c r="F7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>21.1%</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>7</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>6</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>6</v>
+      </c>
+      <c r="R7" t="n">
+        <v>4</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S6"/>
+  <autoFilter ref="A1:S7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2516,41 +2873,41 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H2" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -2572,29 +2929,29 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="H3" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -2602,111 +2959,111 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SLB_M._SOUSA</t>
+          <t>SLB_T._FILIPE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>M. Sousa</t>
+          <t>T. Filipe</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="H4" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I4" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SLB_T._FILIPE</t>
+          <t>SLB_M._SOUSA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>T. Filipe</t>
+          <t>M. Sousa</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H5" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -2714,18 +3071,18 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -2740,7 +3097,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -2752,36 +3109,36 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -2837,7 +3194,7 @@
         <v>6</v>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -2864,14 +3221,14 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H8" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I8" t="n">
         <v>0.9</v>
@@ -2882,11 +3239,11 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="M8" t="n">
@@ -2955,12 +3312,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SLB_J._CORREIA</t>
+          <t>SLB_G._VIEGAS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>J. Correia</t>
+          <t>G. Viegas</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -2976,7 +3333,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -3005,12 +3362,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SLB_M._GONCALVES</t>
+          <t>SLB_J._CORREIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>M. Goncalves</t>
+          <t>J. Correia</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -3036,11 +3393,11 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -3055,12 +3412,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SLB_G._VIEGAS</t>
+          <t>SLB_M._GONCALVES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>G. Viegas</t>
+          <t>M. Goncalves</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -3076,7 +3433,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -3114,10 +3471,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -3208,61 +3565,229 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SLB_S._SOUSA</t>
+          <t>SLB_M._SOUSA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>S. Sousa</t>
+          <t>M. Sousa</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
         <v>5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="H2" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>4</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SLB_S._SOUSA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>S. Sousa</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>21</v>
+      </c>
+      <c r="D3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>45</v>
+      </c>
+      <c r="H3" t="n">
+        <v>43</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>13</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SLB_J._MENDES</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>J. Mendes</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>15</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>57.7%</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>26</v>
+      </c>
+      <c r="H4" t="n">
+        <v>25</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="K2" t="n">
-        <v>8</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N2" t="n">
+      <c r="K4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
         <v>2</v>
       </c>
+      <c r="N4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SLB_T._FILIPE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>T. Filipe</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>13</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>40.6%</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>32</v>
+      </c>
+      <c r="H5" t="n">
+        <v>23</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>13</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>46.2%</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>3</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N2"/>
+  <autoFilter ref="A1:N5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3341,17 +3866,17 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -3359,7 +3884,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -3376,32 +3901,32 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -3411,25 +3936,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -3442,60 +3967,60 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -3512,21 +4037,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -3534,14 +4059,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3567,7 +4092,7 @@
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
@@ -3672,57 +4197,57 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="G2" t="n">
+        <v>13</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
         <v>8</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>7</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>5</v>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -3746,11 +4271,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -3759,40 +4284,40 @@
         </is>
       </c>
       <c r="G3" t="n">
+        <v>9</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>5</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>20.0%</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="L3" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -3816,11 +4341,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -3829,11 +4354,11 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -3850,34 +4375,34 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SLB_K._DOMINGUES</t>
+          <t>SLB_M._SOUSA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>K. Domingues</t>
+          <t>M. Sousa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3886,86 +4411,86 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="G5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
         <v>3</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>66.7%</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
       <c r="L5" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SLB_M._SOUSA</t>
+          <t>SLB_K._DOMINGUES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M. Sousa</t>
+          <t>K. Domingues</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -3973,40 +4498,40 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="7">
@@ -4022,53 +4547,53 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7" t="n">
+        <v>6</v>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>3</v>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
       <c r="L7" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -4076,7 +4601,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="8">
@@ -4152,30 +4677,30 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SLB_W._SANTOS</t>
+          <t>SLB_G._VIEGAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>W. Santos</t>
+          <t>G. Viegas</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -4190,52 +4715,58 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SLB_J._CORREIA</t>
+          <t>SLB_W._SANTOS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>J. Correia</t>
+          <t>W. Santos</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -4244,54 +4775,48 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SLB_M._GONCALVES</t>
+          <t>SLB_J._CORREIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>M. Goncalves</t>
+          <t>J. Correia</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -4314,12 +4839,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SLB_G._VIEGAS</t>
+          <t>SLB_M._GONCALVES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>G. Viegas</t>
+          <t>M. Goncalves</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -4335,14 +4860,24 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -4369,7 +4904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4459,25 +4994,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -4500,21 +5035,21 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -4522,7 +5057,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -4545,36 +5080,36 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -4594,25 +5129,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -4639,25 +5174,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -4670,140 +5205,365 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SLB_J._MENDES</t>
+          <t>SLB_T._FILIPE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>J. Mendes</t>
+          <t>T. Filipe</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D7" t="n">
+        <v>9</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
         <v>6</v>
       </c>
-      <c r="E7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F7" t="n">
-        <v>8</v>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SLB_S._SOUSA</t>
+          <t>SLB_J._MENDES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>S. Sousa</t>
+          <t>J. Mendes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>30.8%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
         <v>2</v>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>17.9%</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>3</v>
-      </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>SLB_S._SOUSA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>S. Sousa</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>17.8%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SLB_W._OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>W. Oliveira</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>7</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>36.8%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SLB_M._SOUSA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>M. Sousa</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>6</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" t="n">
+        <v>8</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>31.6%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SLB_W._OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>W. Oliveira</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>6</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>31.6%</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SLB_M._SOUSA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>M. Sousa</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>26.3%</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>SLB_T._FILIPE</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>T. Filipe</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>5</v>
       </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>15.6%</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
         <v>3</v>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2</v>
+      <c r="K14" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K9"/>
+  <autoFilter ref="A1:K14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>